--- a/public/exports-with-coowners/29189838.xlsx
+++ b/public/exports-with-coowners/29189838.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="J103">
-        <v>270</v>
+        <v>589</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281954</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,21 +7785,21 @@
         </is>
       </c>
       <c r="J104">
-        <v>589</v>
+        <v>695</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="J105">
-        <v>695</v>
+        <v>721</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>721</v>
+        <v>3216</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>3216</v>
+        <v>442</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>442</v>
+        <v>1538</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J109">
-        <v>1538</v>
+        <v>2669</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
-        <v>2669</v>
+        <v>1683</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>1683</v>
+        <v>1087</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>1087</v>
+        <v>1367</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>1367</v>
+        <v>706</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J114">
-        <v>706</v>
+        <v>1125</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J115">
-        <v>1125</v>
+        <v>1045</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8681,11 +8681,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J116">
-        <v>1045</v>
+        <v>1150</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8756,11 +8756,11 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J117">
-        <v>1150</v>
+        <v>296</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J118">
-        <v>296</v>
+        <v>645</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8906,11 +8906,11 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J119">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,40 +8966,40 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>668</v>
+        <v>265</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9056,15 +9056,15 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J122">
-        <v>293</v>
+        <v>588</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>588</v>
+        <v>271</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>351</v>
+        <v>825</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,40 +9416,40 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J126">
-        <v>825</v>
+        <v>4946</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,30 +9501,30 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>4946</v>
+        <v>6338</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>6338</v>
+        <v>673</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,21 +9660,21 @@
         </is>
       </c>
       <c r="J129">
-        <v>673</v>
+        <v>1800</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>1950</v>
+        <v>4954</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>4954</v>
+        <v>2189</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="J133">
-        <v>2189</v>
+        <v>963</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,21 +10035,21 @@
         </is>
       </c>
       <c r="J134">
-        <v>963</v>
+        <v>1070</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>1070</v>
+        <v>326</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,40 +10166,40 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,40 +10241,40 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>294</v>
+        <v>1558</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J139">
-        <v>1558</v>
+        <v>348</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>348</v>
+        <v>2285</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>2285</v>
+        <v>285</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J142">
-        <v>285</v>
+        <v>649</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J143">
-        <v>649</v>
+        <v>1337</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J144">
-        <v>1337</v>
+        <v>461</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J145">
-        <v>461</v>
+        <v>396</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>396</v>
+        <v>2208</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>2208</v>
+        <v>353</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>353</v>
+        <v>8186</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J149">
-        <v>8186</v>
+        <v>586</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J150">
-        <v>586</v>
+        <v>665</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>665</v>
+        <v>1625</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11381,15 +11381,15 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>1625</v>
+        <v>339</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11456,15 +11456,15 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J153">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>348</v>
+        <v>950</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>950</v>
+        <v>1255</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>1255</v>
+        <v>1422</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11756,11 +11756,11 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J157">
-        <v>1422</v>
+        <v>962</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11831,11 +11831,11 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J158">
-        <v>962</v>
+        <v>1499</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J159">
-        <v>1499</v>
+        <v>1232</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J160">
-        <v>1232</v>
+        <v>838</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12056,11 +12056,11 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J161">
-        <v>838</v>
+        <v>587</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12131,11 +12131,11 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J162">
-        <v>587</v>
+        <v>412</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
@@ -12356,11 +12356,11 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="J165">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejen Kommune</t>
+          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12416,40 +12416,40 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Åparken 2A</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">311256, 311257</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>328</v>
+        <v>1815</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311725923</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åparken 2A</t>
+          <t xml:space="preserve">Blomsterengen 13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256, 311257</t>
+          <t xml:space="preserve">311236, 311238, 311237</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>1815</v>
+        <v>2513</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725923</t>
+          <t xml:space="preserve">311727228</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
+          <t xml:space="preserve">Vejen Kommune</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 13</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236, 311238, 311237</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J168">
-        <v>2513</v>
+        <v>912</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727228</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Drejervej 7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>912</v>
+        <v>2188</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 7</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="J170">
-        <v>2188</v>
+        <v>294</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,17 +12791,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Vestergade 19</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,21 +12810,21 @@
         </is>
       </c>
       <c r="J171">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejen Kommune</t>
+          <t xml:space="preserve">Region Syddanmark</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -12866,17 +12866,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 19</t>
+          <t xml:space="preserve">Fredensvej 3C</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">311173, 311174, 311175</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,21 +12885,21 @@
         </is>
       </c>
       <c r="J172">
-        <v>315</v>
+        <v>6738</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311894907</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region Syddanmark</t>
+          <t xml:space="preserve">Vejen Kommune</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -12941,17 +12941,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3C</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173, 311174, 311175</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,16 +12960,16 @@
         </is>
       </c>
       <c r="J173">
-        <v>6738</v>
+        <v>2243</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894907</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13031,15 +13031,15 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J174">
-        <v>2243</v>
+        <v>3900</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,17 +13091,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Møllevænget 5</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>3900</v>
+        <v>2050</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 5</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J176">
-        <v>2050</v>
+        <v>537</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311894879</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J177">
-        <v>537</v>
+        <v>423</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894879</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13331,15 +13331,15 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J178">
-        <v>423</v>
+        <v>1665</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13406,15 +13406,15 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J179">
-        <v>1665</v>
+        <v>273</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>273</v>
+        <v>953</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,17 +13541,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>953</v>
+        <v>1868</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Lindevej 7A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="J182">
-        <v>1868</v>
+        <v>1348</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311914611</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,30 +13691,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7A</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>1348</v>
+        <v>452</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>452</v>
+        <v>1052</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Søndergyden 17</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>1052</v>
+        <v>1782</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergyden 17</t>
+          <t xml:space="preserve">Byagervej 3</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J186">
-        <v>1782</v>
+        <v>2937</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>2937</v>
+        <v>6676</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14081,15 +14081,15 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>6676</v>
+        <v>2183</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J189">
-        <v>2183</v>
+        <v>310</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14231,15 +14231,15 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J190">
-        <v>310</v>
+        <v>907</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14306,15 +14306,15 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J191">
-        <v>907</v>
+        <v>1135</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14381,15 +14381,15 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J192">
-        <v>1135</v>
+        <v>1397</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Petersmindevej 2A</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,30 +14451,30 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">9203884</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="J193">
-        <v>1397</v>
+        <v>1872</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311922670</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 2A</t>
+          <t xml:space="preserve">Lille Veumvej 6</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9203884</t>
+          <t xml:space="preserve">5031183</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>1872</v>
+        <v>1056</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922670</t>
+          <t xml:space="preserve">311923191</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Veumvej 6</t>
+          <t xml:space="preserve">Ø. Skibelundvej 15</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031183</t>
+          <t xml:space="preserve">5039005</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>1056</v>
+        <v>326</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923191</t>
+          <t xml:space="preserve">311923198</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø. Skibelundvej 15</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039005</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>326</v>
+        <v>656</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923198</t>
+          <t xml:space="preserve">311924085</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>656</v>
+        <v>555</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924085</t>
+          <t xml:space="preserve">311925241</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>555</v>
+        <v>443</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925241</t>
+          <t xml:space="preserve">311925148</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>443</v>
+        <v>765</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925148</t>
+          <t xml:space="preserve">311925437</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>765</v>
+        <v>270</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925437</t>
+          <t xml:space="preserve">311926101</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">

--- a/public/exports-with-coowners/29189838.xlsx
+++ b/public/exports-with-coowners/29189838.xlsx
@@ -7466,17 +7466,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>1006</v>
+        <v>589</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,40 +7541,40 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>1360</v>
+        <v>695</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,40 +7616,40 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>536</v>
+        <v>721</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>589</v>
+        <v>3216</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,21 +7785,21 @@
         </is>
       </c>
       <c r="J104">
-        <v>695</v>
+        <v>442</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J105">
-        <v>721</v>
+        <v>1538</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J106">
-        <v>3216</v>
+        <v>2669</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
-        <v>442</v>
+        <v>1683</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>1538</v>
+        <v>1087</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>2669</v>
+        <v>1367</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,30 +8216,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>1683</v>
+        <v>706</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J111">
-        <v>1087</v>
+        <v>1125</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J112">
-        <v>1367</v>
+        <v>1045</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J113">
-        <v>706</v>
+        <v>1150</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J114">
-        <v>1125</v>
+        <v>296</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
-        <v>1045</v>
+        <v>645</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8681,11 +8681,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J116">
-        <v>1150</v>
+        <v>668</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,40 +8741,40 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J117">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,40 +8816,40 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>645</v>
+        <v>293</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,21 +8910,21 @@
         </is>
       </c>
       <c r="J119">
-        <v>668</v>
+        <v>588</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>588</v>
+        <v>825</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,40 +9191,40 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J123">
-        <v>271</v>
+        <v>4946</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="J124">
-        <v>351</v>
+        <v>6338</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,21 +9360,21 @@
         </is>
       </c>
       <c r="J125">
-        <v>825</v>
+        <v>673</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,40 +9416,40 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>4946</v>
+        <v>1800</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,21 +9510,21 @@
         </is>
       </c>
       <c r="J127">
-        <v>6338</v>
+        <v>1950</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>673</v>
+        <v>4954</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>1800</v>
+        <v>2189</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,21 +9735,21 @@
         </is>
       </c>
       <c r="J130">
-        <v>1950</v>
+        <v>963</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>4954</v>
+        <v>1070</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,30 +9866,30 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
-        <v>2189</v>
+        <v>326</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="J133">
-        <v>963</v>
+        <v>325</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,30 +10016,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J134">
-        <v>1070</v>
+        <v>294</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>326</v>
+        <v>1558</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,40 +10166,40 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J136">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>294</v>
+        <v>2285</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J138">
-        <v>1558</v>
+        <v>285</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J139">
-        <v>348</v>
+        <v>649</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J140">
-        <v>2285</v>
+        <v>1337</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J141">
-        <v>285</v>
+        <v>461</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J142">
-        <v>649</v>
+        <v>396</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>1337</v>
+        <v>2208</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>461</v>
+        <v>353</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J145">
-        <v>396</v>
+        <v>8186</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J146">
-        <v>2208</v>
+        <v>586</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J147">
-        <v>353</v>
+        <v>665</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>8186</v>
+        <v>1625</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>586</v>
+        <v>339</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J150">
-        <v>665</v>
+        <v>348</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>1625</v>
+        <v>950</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>339</v>
+        <v>1255</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>348</v>
+        <v>1422</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J154">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J155">
-        <v>1255</v>
+        <v>1499</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J156">
-        <v>1422</v>
+        <v>1232</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11756,11 +11756,11 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J157">
-        <v>962</v>
+        <v>838</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11831,11 +11831,11 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J158">
-        <v>1499</v>
+        <v>587</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J159">
-        <v>1232</v>
+        <v>412</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11966,40 +11966,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="J160">
-        <v>838</v>
+        <v>328</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejen Kommune</t>
+          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Åparken 2A</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,30 +12051,30 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">311256, 311257</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>587</v>
+        <v>1815</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311725923</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12101,12 +12101,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejen Kommune</t>
+          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Blomsterengen 13</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,30 +12126,30 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">311236, 311238, 311237</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>412</v>
+        <v>2513</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311727228</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>386</v>
+        <v>912</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Drejervej 7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,21 +12285,21 @@
         </is>
       </c>
       <c r="J164">
-        <v>386</v>
+        <v>2188</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,30 +12351,30 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
+          <t xml:space="preserve">Vejen Kommune</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åparken 2A</t>
+          <t xml:space="preserve">Vestergade 19</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256, 311257</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="J166">
-        <v>1815</v>
+        <v>315</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725923</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOLSTED BOLIGFORENING</t>
+          <t xml:space="preserve">Region Syddanmark</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 13</t>
+          <t xml:space="preserve">Fredensvej 3C</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236, 311238, 311237</t>
+          <t xml:space="preserve">311173, 311174, 311175</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,21 +12510,21 @@
         </is>
       </c>
       <c r="J167">
-        <v>2513</v>
+        <v>6738</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727228</t>
+          <t xml:space="preserve">311894907</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,40 +12566,40 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>912</v>
+        <v>2243</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,40 +12641,40 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 7</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>2188</v>
+        <v>3900</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,40 +12716,40 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Møllevænget 5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>294</v>
+        <v>2050</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,40 +12791,40 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 19</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J171">
-        <v>315</v>
+        <v>537</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311894879</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region Syddanmark</t>
+          <t xml:space="preserve">Vejen Kommune</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -12866,40 +12866,40 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3C</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173, 311174, 311175</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>6738</v>
+        <v>423</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894907</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
-        <v>2243</v>
+        <v>1665</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J174">
-        <v>3900</v>
+        <v>273</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 5</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>2050</v>
+        <v>953</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>537</v>
+        <v>1868</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894879</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Lindevej 7A</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="J177">
-        <v>423</v>
+        <v>1348</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311914611</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>1665</v>
+        <v>452</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>273</v>
+        <v>1052</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Søndergyden 17</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>953</v>
+        <v>1782</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,30 +13541,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Byagervej 3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
-        <v>1868</v>
+        <v>2937</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7A</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>1348</v>
+        <v>6676</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,30 +13691,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>452</v>
+        <v>2183</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J184">
-        <v>1052</v>
+        <v>310</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergyden 17</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J185">
-        <v>1782</v>
+        <v>907</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J186">
-        <v>2937</v>
+        <v>1135</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14006,15 +14006,15 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J187">
-        <v>6676</v>
+        <v>1397</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Petersmindevej 2A</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,30 +14076,30 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">9203884</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="J188">
-        <v>2183</v>
+        <v>1872</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311922670</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,30 +14141,30 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Lille Veumvej 6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5031183</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189">
-        <v>310</v>
+        <v>1056</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311923191</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Ø. Skibelundvej 15</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5039005</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>907</v>
+        <v>326</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311923198</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>1135</v>
+        <v>656</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311924085</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J192">
-        <v>1397</v>
+        <v>555</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311925241</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,40 +14441,40 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 2A</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9203884</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J193">
-        <v>1872</v>
+        <v>443</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922670</t>
+          <t xml:space="preserve">311925148</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Veumvej 6</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031183</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>1056</v>
+        <v>765</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923191</t>
+          <t xml:space="preserve">311925437</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø. Skibelundvej 15</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039005</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923198</t>
+          <t xml:space="preserve">311926101</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J196">
-        <v>656</v>
+        <v>386</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924085</t>
+          <t xml:space="preserve">311926710</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>555</v>
+        <v>386</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925241</t>
+          <t xml:space="preserve">311926704</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>443</v>
+        <v>1006</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925148</t>
+          <t xml:space="preserve">311928157</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J199">
-        <v>765</v>
+        <v>1360</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925437</t>
+          <t xml:space="preserve">311928163</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,30 +14966,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J200">
-        <v>270</v>
+        <v>536</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926101</t>
+          <t xml:space="preserve">311928160</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-09-25</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
